--- a/126-node case/ResourceParameter.xlsx
+++ b/126-node case/ResourceParameter.xlsx
@@ -12,7 +12,7 @@
     <sheet name="ESS" sheetId="3" r:id="rId3"/>
     <sheet name="FL" sheetId="4" r:id="rId4"/>
     <sheet name="Price" sheetId="5" r:id="rId5"/>
-    <sheet name="SOC" sheetId="6" r:id="rId6"/>
+    <sheet name="SOP" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
